--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.68 ± 0.06</t>
+          <t>0.72 ± 0.06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.58 ± 0.07</t>
+          <t>0.61 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.08</t>
+          <t>0.57 ± 0.11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.63 ± 0.16</t>
+          <t>0.73 ± 0.12</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,12 +498,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.79 ± 0.12</t>
+          <t>0.66 ± 0.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.60 ± 0.20</t>
+          <t>0.74 ± 0.17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
